--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136241532</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136241534</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>136241536</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136241537</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136241538</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>136241549</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136241551</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136241555</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136241541</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>136241543</v>
       </c>
       <c r="B12" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>136241553</v>
       </c>
       <c r="B13" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136241532</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136241534</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>136241536</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136241537</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136241538</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>136241549</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136241551</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136241555</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136241541</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>136241543</v>
       </c>
       <c r="B12" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>136241553</v>
       </c>
       <c r="B13" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -821,11 +821,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -943,11 +939,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1065,11 +1057,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1187,11 +1175,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1309,11 +1293,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1431,11 +1411,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1553,11 +1529,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1675,11 +1647,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1797,11 +1765,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -1914,11 +1878,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>
@@ -2031,11 +1991,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klöverberg, Nb</t>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136241532</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136241534</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136241536</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136241537</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>136241538</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136241549</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136241551</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136241555</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136241541</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136241543</v>
       </c>
       <c r="B12" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136241553</v>
       </c>
       <c r="B13" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136241532</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136241534</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136241536</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136241537</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>136241538</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136241549</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136241551</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136241555</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136241541</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136241543</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136241553</v>
       </c>
       <c r="B13" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60444-2025 artfynd.xlsx
+++ b/artfynd/A 60444-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136241535</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136241532</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136241534</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136241536</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136241537</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>136241538</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136241549</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136241551</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136241555</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136241541</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136241543</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136241553</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>136241539</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136241540</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136241544</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>136241545</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>136241546</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136241548</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136241552</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>136241554</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>136241557</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
